--- a/results/job_matches_2026-07-03.xlsx
+++ b/results/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DBT Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barnes Aerospace</t>
+          <t>OSI Digital</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Google Cloud Platform, Scala, Snowflake, Time Travel, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6c863fad4f5188</t>
+          <t>https://www.indeed.com/viewjob?jk=c8765bd1c65b5570</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Customer Data Products)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Barnes Aerospace</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Step Functions, RDS, Hadoop, Hive, MapReduce, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce51fb4ed88355c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6c863fad4f5188</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Customer Data Products)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dorleco</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, Step Functions, RDS, Hadoop, Hive, MapReduce, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2316c19c169e1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cce51fb4ed88355c</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Developer/Sr Developer, IT Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Dorleco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9553c5cf6b0e55e</t>
+          <t>https://www.indeed.com/viewjob?jk=e2316c19c169e1b3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Advisor Software Engineer (AI/ML)</t>
+          <t>Developer/Sr Developer, IT Applications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76ab24dd411e42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b9553c5cf6b0e55e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Data Platform Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAVISHTY</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Impala, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5de4f159f9c510</t>
+          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>SAVISHTY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Impala, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5de4f159f9c510</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake/DataStage)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
+          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer (Snowflake/DataStage)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nlineaxis It Solutions</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcac5ba7033fe638</t>
+          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Nlineaxis It Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=bcac5ba7033fe638</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[P] Data Engineer, Safeguards</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
+          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
         </is>
       </c>
     </row>
@@ -1203,52 +1203,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Career Team Enterprises</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
+          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Career Team Enterprises</t>
+          <t>QUARTERMASTER</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>QUARTERMASTER</t>
+          <t>Career TEAM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
+          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>IT Architect (ADI)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Career TEAM</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Architect (ADI)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Blue Cross and Blue Shield of Kansas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
+          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer - Senior Application Development Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Kansas</t>
+          <t>Idaho Power Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
+          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Data Specialist (US)</t>
+          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Polars, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52604e251f7f7ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Application Development Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Idaho Power Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5540a404124c7a</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5540a404124c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=667f77c9d7a9c12e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667f77c9d7a9c12e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9629f01e9f1302a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9629f01e9f1302a</t>
+          <t>https://www.indeed.com/viewjob?jk=e41e55af397dabdd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
+          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41e55af397dabdd</t>
+          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
+          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
+          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
+          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Engineer, DevOps/Platform Reliability</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>PayCargo LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
+          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps/Platform Reliability</t>
+          <t>Senior Software Engineer- Generative AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PayCargo LLC</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
+          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>QA Automation Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Generative AI</t>
+          <t>Senior Information Services Developer- Databricks</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II</t>
+          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
+          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
+          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>American Civil Liberties Union</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Information Services Developer- Databricks</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
+          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Big Data / AWS Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ICT Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>The Hillman Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
+          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ICT Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
+          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
         </is>
       </c>
     </row>
@@ -2533,25 +2533,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer, Sportsbook Platform</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
+          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
+          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer, Sportsbook Platform</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
+          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sunsoft Services Inc</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
+          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Database &amp; Data Platform Administrator</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Colorado Public Employees' Retirement Association</t>
+          <t>Sunsoft Services Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database &amp; Data Platform Administrator</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wyoming, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
+          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wyoming, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
+          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
+          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
+          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
+          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MGR - SOFTWARE ENGINEERING</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sunrise Banks</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>MGR - SOFTWARE ENGINEERING</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
+          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,15 +3251,50 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Alarm.com</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tysons Corner, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
         </is>

--- a/results/job_matches_2026-07-03.xlsx
+++ b/results/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c12624733c865304</t>
+          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Snowflake/DataStage)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake/DataStage)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>Nlineaxis It Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
+          <t>https://www.indeed.com/viewjob?jk=bcac5ba7033fe638</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer - Spark, Hadoop, Ozone CH, Flink | Berkley Heights, NJ (Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nlineaxis It Solutions</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcac5ba7033fe638</t>
+          <t>https://www.indeed.com/viewjob?jk=54cabd90bb4fcf14</t>
         </is>
       </c>
     </row>
@@ -963,47 +963,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Spark, Hadoop, Ozone CH, Flink | Berkley Heights, NJ (Onsite) | Contract W2 only</t>
+          <t>Senior Technical Specialist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cabd90bb4fcf14</t>
+          <t>https://www.indeed.com/viewjob?jk=16c83b1e95fee975</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Full Stack Developer (Senior)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5be43041964a628</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Technical Specialist</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c83b1e95fee975</t>
+          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Production Engineer (Contract)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>VantageScore</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, GCP, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5be43041964a628</t>
+          <t>https://www.indeed.com/viewjob?jk=16eab15177302646</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Career Team Enterprises</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Production Engineer (Contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VantageScore</t>
+          <t>QUARTERMASTER</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, GCP, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16eab15177302646</t>
+          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Career Team Enterprises</t>
+          <t>Career TEAM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Architect (ADI)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>QUARTERMASTER</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Career TEAM</t>
+          <t>Blue Cross and Blue Shield of Kansas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT Architect (ADI)</t>
+          <t>Data Engineer - Senior Application Development Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Idaho Power Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Kansas</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
+          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Application Development Analyst</t>
+          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Idaho Power Company</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
+          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5540a404124c7a</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5540a404124c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=667f77c9d7a9c12e</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667f77c9d7a9c12e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9629f01e9f1302a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9629f01e9f1302a</t>
+          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
         </is>
       </c>
     </row>
@@ -1938,25 +1938,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II</t>
+          <t>Senior Information Services Developer- Databricks</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
+          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Information Services Developer- Databricks</t>
+          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
+          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
+          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>American Civil Liberties Union</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Civil Liberties Union</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
+          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Big Data / AWS Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Big Data / AWS Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>The Hillman Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
+          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>ICT Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ICT Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>The Hillman Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
+          <t>https://www.indeed.com/viewjob?jk=9726119dcb779aff</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer, Sportsbook Platform</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Software Engineer, Sportsbook Platform</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
+          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
+          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sunsoft Services Inc</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
+          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Database &amp; Data Platform Administrator</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Colorado Public Employees' Retirement Association</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
+          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Sunsoft Services Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wyoming, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database &amp; Data Platform Administrator</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
+          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Wyoming, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
+          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
+          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
+          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
+          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Database Engineer (DBRE)</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,42 +3076,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dac21e8c2033fca7</t>
+          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Database Engineer (DBRE)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
+          <t>https://www.indeed.com/viewjob?jk=dac21e8c2033fca7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
+          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MGR - SOFTWARE ENGINEERING</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sunrise Banks</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
+          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MGR - SOFTWARE ENGINEERING</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
+          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,15 +3286,85 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Alarm.com</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tysons Corner, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
         </is>

--- a/results/job_matches_2026-07-03.xlsx
+++ b/results/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAVISHTY</t>
+          <t>Dorleco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580224382e8a12e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e2316c19c169e1b3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer/Sr Developer, IT Applications</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dorleco</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2316c19c169e1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b9553c5cf6b0e55e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Developer/Sr Developer, IT Applications</t>
+          <t>Cloud Data Platform Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Impala, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9553c5cf6b0e55e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Impala, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer (Snowflake/DataStage)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAVISHTY</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5de4f159f9c510</t>
+          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Spark, Hadoop, Ozone CH, Flink | Berkley Heights, NJ (Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=54cabd90bb4fcf14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake/DataStage)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Technical Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nlineaxis It Solutions</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcac5ba7033fe638</t>
+          <t>https://www.indeed.com/viewjob?jk=16c83b1e95fee975</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Spark, Hadoop, Ozone CH, Flink | Berkley Heights, NJ (Onsite) | Contract W2 only</t>
+          <t>Java Full Stack Developer (Senior)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cabd90bb4fcf14</t>
+          <t>https://www.indeed.com/viewjob?jk=c5be43041964a628</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Production Engineer (Contract)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>VantageScore</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, GCP, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=16eab15177302646</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Technical Specialist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Career Team Enterprises</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c83b1e95fee975</t>
+          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>QUARTERMASTER</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5be43041964a628</t>
+          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Career TEAM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Production Engineer (Contract)</t>
+          <t>IT Architect (ADI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VantageScore</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, GCP, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16eab15177302646</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Career Team Enterprises</t>
+          <t>Blue Cross and Blue Shield of Kansas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Senior Application Development Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>QUARTERMASTER</t>
+          <t>Idaho Power Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
+          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Career TEAM</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IT Architect (ADI)</t>
+          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
+          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Kansas</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5540a404124c7a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Application Development Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Idaho Power Company</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,54 +1336,54 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
+          <t>https://www.indeed.com/viewjob?jk=667f77c9d7a9c12e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c9629f01e9f1302a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e41e55af397dabdd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5540a404124c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667f77c9d7a9c12e</t>
+          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9629f01e9f1302a</t>
+          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41e55af397dabdd</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
+          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
+          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
+          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
+          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Engineer, DevOps/Platform Reliability</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>PayCargo LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer- Generative AI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Information Services Developer- Databricks</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
+          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps/Platform Reliability</t>
+          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PayCargo LLC</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
+          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Generative AI</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Information Services Developer- Databricks</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>American Civil Liberties Union</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
+          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
+          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Big Data / AWS Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Civil Liberties Union</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>The Hillman Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>ICT Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
+          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Big Data / AWS Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>The Hillman Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=9726119dcb779aff</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ICT Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9726119dcb779aff</t>
+          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr Engineer, BI - Onsite</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,77 +2376,77 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
+          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer, Sportsbook Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,94 +2456,94 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Engineer, BI - Onsite</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer, Sportsbook Platform</t>
+          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
+          <t>https://www.indeed.com/viewjob?jk=81913d589c038b43</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Wyoming, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
+          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
+          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Sunsoft Services Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Database &amp; Data Platform Administrator</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
+          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sunsoft Services Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Database &amp; Data Platform Administrator</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Colorado Public Employees' Retirement Association</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
+          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wyoming, MI, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
+          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
+          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,137 +2981,137 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
+          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
+          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>MGR - SOFTWARE ENGINEERING</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
+          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Database Engineer (DBRE)</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, ETL, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dac21e8c2033fca7</t>
+          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
+          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,190 +3181,15 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>MGR - SOFTWARE ENGINEERING</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Sunrise Banks</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Frontend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Alarm.com</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Tysons Corner, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
         </is>

--- a/results/job_matches_2026-07-03.xlsx
+++ b/results/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Customer Data Products)</t>
+          <t>Developer/Sr Developer, IT Applications</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Step Functions, RDS, Hadoop, Hive, MapReduce, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce51fb4ed88355c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9553c5cf6b0e55e</t>
         </is>
       </c>
     </row>
@@ -648,20 +648,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dorleco</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2316c19c169e1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Developer/Sr Developer, IT Applications</t>
+          <t>Data Engineer (Snowflake/DataStage)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9553c5cf6b0e55e</t>
+          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Architect</t>
+          <t>Data Engineer - Spark, Hadoop, Ozone CH, Flink | Berkley Heights, NJ (Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Impala, Spark</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=54cabd90bb4fcf14</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake/DataStage)</t>
+          <t>Senior Technical Specialist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
+          <t>https://www.indeed.com/viewjob?jk=16c83b1e95fee975</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Spark, Hadoop, Ozone CH, Flink | Berkley Heights, NJ (Onsite) | Contract W2 only</t>
+          <t>Java Full Stack Developer (Senior)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cabd90bb4fcf14</t>
+          <t>https://www.indeed.com/viewjob?jk=c5be43041964a628</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Production Engineer (Contract)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>VantageScore</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, GCP, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=16eab15177302646</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Technical Specialist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Career Team Enterprises</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c83b1e95fee975</t>
+          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>QUARTERMASTER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5be43041964a628</t>
+          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Production Engineer (Contract)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VantageScore</t>
+          <t>Career TEAM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, GCP, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16eab15177302646</t>
+          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>IT Architect (ADI)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Career Team Enterprises</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>QUARTERMASTER</t>
+          <t>Blue Cross and Blue Shield of Kansas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
+          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Senior Application Development Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Career TEAM</t>
+          <t>Idaho Power Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IT Architect (ADI)</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
+          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Kansas</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Application Development Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Idaho Power Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,54 +1196,54 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5540a404124c7a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e41e55af397dabdd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5540a404124c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667f77c9d7a9c12e</t>
+          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9629f01e9f1302a</t>
+          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41e55af397dabdd</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
+          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Engineer, DevOps/Platform Reliability</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>PayCargo LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
+          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
+          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer- Generative AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Information Services Developer- Databricks</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
+          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
+          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps/Platform Reliability</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PayCargo LLC</t>
+          <t>American Civil Liberties Union</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
+          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Generative AI</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Information Services Developer- Databricks</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
+          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
+          <t>Big Data / AWS Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>The Hillman Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>ICT Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,102 +1931,102 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Civil Liberties Union</t>
+          <t>The Hillman Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
+          <t>https://www.indeed.com/viewjob?jk=9726119dcb779aff</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Software Engineer II - Python</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Big Data / AWS Software Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
+          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ICT Data Engineer</t>
+          <t>Sr Engineer, BI - Onsite</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,77 +2166,77 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9726119dcb779aff</t>
+          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer, Sportsbook Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
+          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
+          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,59 +2351,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Engineer, BI - Onsite</t>
+          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,29 +2411,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
+          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer, Sportsbook Platform</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Sunsoft Services Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Database &amp; Data Platform Administrator</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
+          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Wyoming, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81913d589c038b43</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wyoming, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
+          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
+          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
+          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sunsoft Services Inc</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
+          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Database &amp; Data Platform Administrator</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Colorado Public Employees' Retirement Association</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
+          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,129 +2841,129 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>MGR - SOFTWARE ENGINEERING</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
+          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
+          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
+          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2980,216 +2980,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Data Analyst / Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>McAfee</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>MGR - SOFTWARE ENGINEERING</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Sunrise Banks</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Frontend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Alarm.com</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Tysons Corner, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
         </is>

--- a/results/job_matches_2026-07-03.xlsx
+++ b/results/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DBT Developer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OSI Digital</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Google Cloud Platform, Scala, Snowflake, Time Travel, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8765bd1c65b5570</t>
+          <t>https://www.indeed.com/viewjob?jk=3375df1916d0dbd2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DBT Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Barnes Aerospace</t>
+          <t>OSI Digital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Google Cloud Platform, Scala, Snowflake, Time Travel, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6c863fad4f5188</t>
+          <t>https://www.indeed.com/viewjob?jk=c8765bd1c65b5570</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Developer/Sr Developer, IT Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Barnes Aerospace</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9553c5cf6b0e55e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6c863fad4f5188</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer/Sr Developer, IT Applications</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b9553c5cf6b0e55e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake/DataStage)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
+          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Spark, Hadoop, Ozone CH, Flink | Berkley Heights, NJ (Onsite) | Contract W2 only</t>
+          <t>Data Engineer (Snowflake/DataStage)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cabd90bb4fcf14</t>
+          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Spark, Hadoop, Ozone CH, Flink | Berkley Heights, NJ (Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=54cabd90bb4fcf14</t>
         </is>
       </c>
     </row>
@@ -1553,25 +1553,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Generative AI</t>
+          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Information Services Developer- Databricks</t>
+          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
+          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
+          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>American Civil Liberties Union</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Civil Liberties Union</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
+          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Big Data / AWS Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>The Hillman Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
+          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Big Data / AWS Software Engineer</t>
+          <t>ICT Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
         </is>
       </c>
     </row>
@@ -1891,29 +1891,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9726119dcb779aff</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ICT Data Engineer</t>
+          <t>Senior Software Engineer - SRE Focus</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer II - Python</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9726119dcb779aff</t>
+          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
+          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
+          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr Engineer, BI - Onsite</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,69 +2131,69 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Engineer, BI - Onsite</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Software Engineer, Sportsbook Platform</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
+          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer, Sportsbook Platform</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
+          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
+          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wyoming, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
+          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sunsoft Services Inc</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
+          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Database &amp; Data Platform Administrator</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Colorado Public Employees' Retirement Association</t>
+          <t>Sunsoft Services Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database &amp; Data Platform Administrator</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wyoming, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
+          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
+          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,94 +2666,94 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
+          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
+          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
+          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>MGR - SOFTWARE ENGINEERING</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
+          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MGR - SOFTWARE ENGINEERING</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sunrise Banks</t>
+          <t>Awesome Motive Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,122 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Frontend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Alarm.com</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Tysons Corner, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
+          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-03.xlsx
+++ b/results/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Developer/Sr Developer, IT Applications</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9553c5cf6b0e55e</t>
+          <t>https://www.indeed.com/viewjob?jk=c12624733c865304</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Application Development Analyst</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Idaho Power Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,64 +1081,64 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
+          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5540a404124c7a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e41e55af397dabdd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5540a404124c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Senior Engineer, DevOps/Platform Reliability</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>PayCargo LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41e55af397dabdd</t>
+          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
+          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
+          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
+          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps/Platform Reliability</t>
+          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PayCargo LLC</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
+          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
+          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>American Civil Liberties Union</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
+          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Big Data / AWS Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Civil Liberties Union</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Hudson River Community Credit Union</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Corinth, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>The Hillman Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
+          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Big Data / AWS Software Engineer</t>
+          <t>ICT Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer II - Python</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
+          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ICT Data Engineer</t>
+          <t>Senior Software Engineer - SRE Focus</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9726119dcb779aff</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE Focus</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
+          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
+          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Sr Engineer, BI - Onsite</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,77 +2026,77 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer, Sportsbook Platform</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Engineer, BI - Onsite</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
+          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer, Sportsbook Platform</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
+          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wyoming, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
+          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Sunsoft Services Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wyoming, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Database &amp; Data Platform Administrator</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
+          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sunsoft Services Inc</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
+          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Database &amp; Data Platform Administrator</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Colorado Public Employees' Retirement Association</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
+          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,139 +2551,139 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
+          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>MGR - SOFTWARE ENGINEERING - HYBRID ROLE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
+          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
+          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Awesome Motive Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,155 +2726,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>MGR - SOFTWARE ENGINEERING</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Sunrise Banks</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Frontend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Awesome Motive Inc.</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Miami Beach, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
         </is>

--- a/results/job_matches_2026-07-03.xlsx
+++ b/results/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,20 +613,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Barnes Aerospace</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6c863fad4f5188</t>
+          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer - Spark, Hadoop, Ozone CH, Flink | Berkley Heights, NJ (Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c12624733c865304</t>
+          <t>https://www.indeed.com/viewjob?jk=54cabd90bb4fcf14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Technical Specialist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=16c83b1e95fee975</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake/DataStage)</t>
+          <t>Java Full Stack Developer (Senior)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
+          <t>https://www.indeed.com/viewjob?jk=c5be43041964a628</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Spark, Hadoop, Ozone CH, Flink | Berkley Heights, NJ (Onsite) | Contract W2 only</t>
+          <t>Production Engineer (Contract)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>VantageScore</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, GCP, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cabd90bb4fcf14</t>
+          <t>https://www.indeed.com/viewjob?jk=16eab15177302646</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Technical Specialist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Career Team Enterprises</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c83b1e95fee975</t>
+          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>QUARTERMASTER</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5be43041964a628</t>
+          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Production Engineer (Contract)</t>
+          <t>IT Architect (ADI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VantageScore</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, GCP, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16eab15177302646</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Career Team Enterprises</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>QUARTERMASTER</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
+          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer, DevOps/Platform Reliability</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Career TEAM</t>
+          <t>PayCargo LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT Architect (ADI)</t>
+          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Kansas</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
+          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Civil Liberties Union</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5540a404124c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41e55af397dabdd</t>
+          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps/Platform Reliability</t>
+          <t>Big Data / AWS Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PayCargo LLC</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Hudson River Community Credit Union</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Corinth, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>The Hillman Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
+          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer - SRE Focus</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer II - Python</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
+          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
+          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Civil Liberties Union</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,46 +1567,46 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
+          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wyoming, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,207 +1651,207 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Big Data / AWS Software Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hudson River Community Credit Union</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Corinth, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
+          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
+          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ICT Data Engineer</t>
+          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Tricon Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
+          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE Focus</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,845 +1896,110 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
+          <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>MGR - SOFTWARE ENGINEERING - HYBRID ROLE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
+          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Awesome Motive Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Sr Engineer, BI - Onsite</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Bass Pro Shops</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Software Engineer, Sportsbook Platform</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Penn Interactive Ventures</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Full Stack Software Developer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>McAfee</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Logisnext Americas Inc</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Logisnext Americas Inc</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Snowflake Architect</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Data Ninjas Inc.</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Gordon Food Service</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Wyoming, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Gordon Food Service</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Sunsoft Services Inc</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Database &amp; Data Platform Administrator</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Colorado Public Employees' Retirement Association</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Data Analyst / Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>McAfee</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MGR - SOFTWARE ENGINEERING - HYBRID ROLE</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Sunrise Banks</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Frontend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Awesome Motive Inc.</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Miami Beach, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
         </is>

--- a/results/job_matches_2026-07-03.xlsx
+++ b/results/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Climb</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps/Platform Reliability</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PayCargo LLC</t>
+          <t>Climb</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
+          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
+          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Civil Liberties Union</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
+          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>American Civil Liberties Union</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE Focus</t>
+          <t>Software Engineer II - Python</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
+          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python</t>
+          <t>Senior Software Engineer - SRE Focus</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
+          <t>https://www.indeed.com/viewjob?jk=cc379557ac7b50a7</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MGR - SOFTWARE ENGINEERING - HYBRID ROLE</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sunrise Banks</t>
+          <t>Awesome Motive Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1965,41 +1965,6 @@
         </is>
       </c>
       <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Awesome Motive Inc.</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Miami Beach, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
         </is>

--- a/results/job_matches_2026-07-03.xlsx
+++ b/results/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Spark, Hadoop, Ozone CH, Flink | Berkley Heights, NJ (Onsite) | Contract W2 only</t>
+          <t>Senior Technical Specialist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cabd90bb4fcf14</t>
+          <t>https://www.indeed.com/viewjob?jk=16c83b1e95fee975</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Technical Specialist</t>
+          <t>Java Full Stack Developer (Senior)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c83b1e95fee975</t>
+          <t>https://www.indeed.com/viewjob?jk=c5be43041964a628</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Career Team Enterprises</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5be43041964a628</t>
+          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Production Engineer (Contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VantageScore</t>
+          <t>QUARTERMASTER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, GCP, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16eab15177302646</t>
+          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>IT Architect (ADI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Career Team Enterprises</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90b2f930cb110ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>QUARTERMASTER</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,77 +836,77 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
+          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT Architect (ADI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Climb</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9d3910b5fff7ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Climb</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78392f2d9015aeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Climb</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f49fab7756cd40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
         </is>
       </c>
     </row>
@@ -963,82 +963,82 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Climb</t>
+          <t>American Civil Liberties Union</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b506ee2b284700</t>
+          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, API Gateway, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
+          <t>https://www.indeed.com/viewjob?jk=22049ffcc6bb4062</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Spark, Scala, Spark Streaming, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b9f6c24003c9c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Big Data / AWS Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Civil Liberties Union</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>Hudson River Community Credit Union</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Corinth, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>The Hillman Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e63eb9663e81846</t>
+          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Big Data / AWS Software Engineer</t>
+          <t>Software Engineer II - Python</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, Scala, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hudson River Community Credit Union</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Corinth, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,147 +1256,147 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Hillman Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f14f82834295e1</t>
+          <t>https://www.indeed.com/viewjob?jk=cc379557ac7b50a7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
+          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE Focus</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9b9608e126cebe</t>
+          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Logisnext Americas Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, Airflow, Python</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc379557ac7b50a7</t>
+          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Data Architect and Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Logisnext Americas Inc</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wyoming, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
+          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wyoming, MI, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
+          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gordon Food Service</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, Data Modeling, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
+          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,19 +1686,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06dfc03b28a69bc</t>
+          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Tricon Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1707,73 +1707,73 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c10f6c53157629</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080d7069ccfb891a</t>
+          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snowflake Architect – AWS &amp; Data Governance | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tricon Solutions</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d27ed14ea847a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
+          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Awesome Motive Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,85 +1886,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Whatfix</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Awesome Motive Inc.</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Miami Beach, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, MLOps, MLflow, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
         </is>
